--- a/output/pdf_financials_xlsx/YES.xlsx
+++ b/output/pdf_financials_xlsx/YES.xlsx
@@ -4684,34 +4684,34 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.163874</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.163874</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0.053744</v>
+        <v>0.204601</v>
       </c>
       <c r="F92" s="3" t="n">
         <v>0.053744</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0.053744</v>
+        <v>0.35564</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0.053744</v>
+        <v>0.466007</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.053744</v>
+        <v>2.648203</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0.053744</v>
+        <v>5.155677</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0.053744</v>
+        <v>7.069555</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0.053744</v>
+        <v>8.327508</v>
       </c>
       <c r="M92" s="1" t="inlineStr">
         <is>
@@ -8366,7 +8366,11 @@
           <t>Share-based payment reserves (note 12)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -10830,7 +10834,11 @@
           <t>Share-based payment reserves (note 13) 7,015,811</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -11950,7 +11958,11 @@
           <t>Share-based payment reserve (note 13)</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -13266,7 +13278,11 @@
           <t>Share-based payment reserves (note 12)</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -16340,7 +16356,11 @@
           <t>Reserves (notes 11 and 12)</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
@@ -18008,7 +18028,11 @@
           <t>Reserves (notes 11 and 12) 150,857</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>
@@ -18708,7 +18732,11 @@
           <t>Reserves (notes 6 and 7)</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/YES.xlsx
+++ b/output/pdf_financials_xlsx/YES.xlsx
@@ -931,10 +931,10 @@
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.125321</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.029322</v>
       </c>
     </row>
     <row r="13">
@@ -1654,10 +1654,10 @@
         <v>-8.434934999999999</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-7.524006</v>
+        <v>-7.649327</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.121188</v>
+        <v>-1.15051</v>
       </c>
     </row>
     <row r="28">
@@ -1744,10 +1744,10 @@
         <v>-7.864953</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-7.000471</v>
+        <v>-7.125792</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.109122</v>
+        <v>-0.138444</v>
       </c>
     </row>
     <row r="30">
@@ -1793,10 +1793,10 @@
         <v>-393.1835610795441</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-221.3940498343451</v>
+        <v>-225.3574008316266</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-4.969917791997814</v>
+        <v>-6.305376539976772</v>
       </c>
     </row>
     <row r="31">
@@ -1912,34 +1912,34 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.984383</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.929131</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.283813</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.831556</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.2832</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.225396</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>3.001384</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.460483</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>2.093154</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.948689</v>
       </c>
       <c r="M34" s="1" t="inlineStr">
         <is>
@@ -2006,34 +2006,34 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.984383</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.929131</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.283813</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.831556</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.2832</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.225396</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>3.001384</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.460483</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>2.093154</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.948689</v>
       </c>
       <c r="M36" s="1" t="inlineStr">
         <is>
@@ -2576,28 +2576,28 @@
         <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.498212</v>
+        <v>0.214399</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.879383</v>
+        <v>0.047827</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.243773</v>
+        <v>0.960573</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.647185</v>
+        <v>0.421789</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>3.53428</v>
+        <v>0.532896</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.004589</v>
+        <v>0.544106</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>6.593001</v>
+        <v>4.499847</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.398281</v>
+        <v>0.449592</v>
       </c>
       <c r="M48" s="1" t="inlineStr">
         <is>
@@ -6118,19 +6118,19 @@
         <v>0</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.057744</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.060952</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.195424</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.345526</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.381</v>
       </c>
     </row>
     <row r="125">
@@ -6163,19 +6163,19 @@
         <v>0</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.057744</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.060952</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.195424</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.345526</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.381</v>
       </c>
     </row>
     <row r="126">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -8982,7 +8982,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -11302,7 +11302,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -13568,7 +13568,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -16740,7 +16740,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -18500,7 +18500,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -20760,7 +20760,11 @@
           <t>Lease payments (note 11)</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -22478,7 +22482,11 @@
           <t>Lease payments (note 10)</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>-</t>
@@ -24392,7 +24400,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -25360,7 +25372,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
@@ -31340,7 +31356,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -32612,7 +32628,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
